--- a/public/Participant_Import_Template.xlsx
+++ b/public/Participant_Import_Template.xlsx
@@ -397,7 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G5"/>
+  <cols>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="25.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,61 +416,116 @@
         <v>Last Name</v>
       </c>
       <c r="C1" t="str">
-        <v>Email (Optional for minors)</v>
+        <v>Email</v>
       </c>
       <c r="D1" t="str">
-        <v>DOB (YYYY-MM-DD) (Optional)</v>
+        <v>Parent Email</v>
       </c>
       <c r="E1" t="str">
-        <v>Address (Optional)</v>
+        <v>DOB</v>
       </c>
       <c r="F1" t="str">
-        <v>Parent Email (Optional)</v>
+        <v>Address</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Same Household As</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Jane</v>
+        <v>John</v>
       </c>
       <c r="B2" t="str">
         <v>Doe</v>
       </c>
       <c r="C2" t="str">
-        <v>jane.doe@example.com</v>
+        <v>john.doe@example.com</v>
       </c>
       <c r="D2" t="str">
-        <v>1980-05-15</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>123 Main St, Anytown</v>
+        <v>1985-03-15</v>
       </c>
       <c r="F2" t="str">
+        <v>123 Main St</v>
+      </c>
+      <c r="G2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>John</v>
+        <v>Jane</v>
       </c>
       <c r="B3" t="str">
         <v>Doe</v>
       </c>
       <c r="C3" t="str">
-        <v/>
+        <v>jane.doe@example.com</v>
       </c>
       <c r="D3" t="str">
-        <v>2010-08-20</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>1987-07-22</v>
       </c>
       <c r="F3" t="str">
-        <v>jane.doe@example.com</v>
+        <v>123 Main St</v>
+      </c>
+      <c r="G3" t="str">
+        <v>John Doe</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Tommy</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Doe</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v>john.doe@example.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v>2015-01-10</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Sarah</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Doe</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
+        <v>john.doe@example.com</v>
+      </c>
+      <c r="E5" t="str">
+        <v>2012-05-20</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G5"/>
   </ignoredErrors>
 </worksheet>
 </file>